--- a/docs/plans/dsh-plugin-tools/iam-response-analysis.xlsx
+++ b/docs/plans/dsh-plugin-tools/iam-response-analysis.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="追问清单" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="矛盾与缺口" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="跨项确认" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与冲突" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'回函分析总表'!$A$4:$K$25</definedName>
@@ -32,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -183,8 +184,15 @@
       <color rgb="00595959"/>
       <sz val="8.5"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -229,6 +237,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -380,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -539,6 +552,19 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -906,7 +932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1110,7 +1136,7 @@
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>本函以 2026-10-26 回函为唯一输入，逐项核对原问询要求、回函结论与可验收证据。回函覆盖 21 项中的 18 项，另 3 项（CONF-IAM-07/17/18）由企业内团队确认，产品方无需答复。</t>
+          <t>本函以 2026-10-26 厂商 21 项回函为基线，并参考同日内部校验回函；两者结论不一致处见“来源与冲突”，不把内部观察升级为厂商承诺。回函覆盖 21 项中的 18 项，另 3 项（CONF-IAM-07/17/18）由企业内团队确认，产品方无需答复。</t>
         </is>
       </c>
       <c r="B17" s="10" t="n"/>
@@ -2018,9 +2044,25 @@
       <c r="E69" s="10" t="n"/>
       <c r="F69" s="11" t="n"/>
     </row>
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" s="59" t="inlineStr">
+        <is>
+          <t>来源与冲突</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="60" t="inlineStr">
+        <is>
+          <t>本工作簿的统计以厂商 21 项回函为基线；内部校验回函 18 项作为部署观察，冲突与采用口径见“来源与冲突”表。两源冲突时取更保守口径，不把未确认能力写成已支持。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="62">
+  <mergeCells count="63">
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C48:F48"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A66:F66"/>
@@ -2044,6 +2086,7 @@
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="C42:F42"/>
     <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A72:F72"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="C32:E32"/>
     <mergeCell ref="C38:E38"/>
@@ -2078,7 +2121,6 @@
     <mergeCell ref="C46:F46"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A69:F69"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="A65:F65"/>
@@ -2213,7 +2255,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>CONF-IAM-08 明确不支持公共客户端与 PKCE，只能退化为机密客户端 + 本机 secret；CONF-IAM-04 明确已签发 AT 无法服务端阻断。前者改变客户端安全模型，后者使“停用五分钟”不能由 IAM 单独保证。</t>
+          <t>CONF-IAM-08：厂商 6.0.3/6.3 回函明确不支持公共客户端与 PKCE；内部校验回函 §02 称 PKCE 能力但 §08 未答，未确认公共客户端。CONF-IAM-04：厂商把“已签发 AT 实时阻断”列为“需产品确认、按不具备规划”；内部回函称账号禁用后 AT/RT 实时作废。两者均为冲突/未证实，V1 只能按保守口径设计。</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2414,7 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>五分钟停用未闭环；公共客户端/PKCE 缺口未决；无 SCIM 出站或等价事件通道。需书面路线图或替代方案后再评。</t>
+          <t>五分钟停用未闭环；公共客户端/PKCE 厂商口径缺口未决；6.0.3 无 SCIM 出站、6.3 仅部分支持。需书面路线图或替代方案后再评。</t>
         </is>
       </c>
       <c r="D19" s="11" t="n"/>
@@ -2673,7 +2715,7 @@
     <row r="7" ht="56.825" customHeight="1">
       <c r="A7" s="55" t="inlineStr">
         <is>
-          <t>两项缺口直接影响 V1 方案：其一，公共客户端与 PKCE 明确不支持，桌面客户端只能退化为机密客户端 + 本机 secret，安全模型与运维方式均需调整；其二，已签发 Access Token 无法服务端阻断，停用与退出后的五分钟要求不能由 IAM 单独保证，必须由短 TTL 与网关回查共同兜底。</t>
+          <t>两项缺口直接影响 V1 方案：其一，厂商回函称公共客户端与 PKCE 不支持；内部回函 §02 称 PKCE 能力、§08 未答，不能推出免 Secret 公共客户端。桌面客户端仍按机密客户端 + 本机 secret 设计。其二，厂商把“已签发 Access Token 服务端阻断”列为按不具备规划；内部回函称账号禁用后实时作废。两者冲突，五分钟要求不能由 IAM 单独保证，必须由短 TTL、网关有效性回查（若可用）与管理台强制下线共同兜底，并以实测为准。</t>
         </is>
       </c>
       <c r="B7" s="52" t="n"/>
@@ -3593,7 +3635,7 @@
       </c>
       <c r="I12" s="44" t="inlineStr">
         <is>
-          <t>V1 安全基线（公共客户端 + PKCE）无法落地；机密客户端 secret 在全组织/多终端如何下发、轮换、吊销、防提取均未答；动态注册、mTLS/DPoP、client_id 粒度、审批 SLA、consent 未答；AIGS 的 PKCE 不能填补 V1。</t>
+          <t>厂商口径下 V1 公共客户端 + PKCE 安全基线无法落地；内部回函未确认公共客户端。机密客户端 secret 在全组织/多终端如何下发、轮换、吊销、防提取均未答；动态注册、mTLS/DPoP、client_id 粒度、审批 SLA、consent 未答；AIGS 的 PKCE 不能填补 V1。</t>
         </is>
       </c>
       <c r="J12" s="44" t="inlineStr">
@@ -7663,7 +7705,7 @@
       </c>
       <c r="C10" s="44" t="inlineStr">
         <is>
-          <t>IAM 明确不支持公共客户端/PKCE；AIGS 页称智能体应用注册原生 PKCE；总表 I 列将 08 标为“AIGS 支持程度=支持”。</t>
+          <t>厂商回函明确不支持公共客户端/PKCE；内部回函 §02 称 PKCE 能力、§08 未答；AIGS 页称智能体应用注册原生 PKCE。三者不是同一层面，不能把 AIGS 的 PKCE 当作 IAM 公共客户端已支持。</t>
         </is>
       </c>
       <c r="D10" s="44" t="inlineStr">
@@ -8281,4 +8323,384 @@
   <pageMargins left="0.3" right="0.3" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="61" t="inlineStr">
+        <is>
+          <t>IAM 回函来源、口径与冲突（2026-10-28）</t>
+        </is>
+      </c>
+      <c r="B1" s="62" t="n"/>
+      <c r="C1" s="62" t="n"/>
+      <c r="D1" s="62" t="n"/>
+      <c r="E1" s="62" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="62" t="inlineStr">
+        <is>
+          <t>原则：以厂商书面版本矩阵为能力基线；内部校验回函作为部署观察，不升级为厂商承诺；两者冲突时取更保守口径，V1 不把未确认能力写成已支持。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="62" t="n"/>
+      <c r="B3" s="62" t="n"/>
+      <c r="C3" s="62" t="n"/>
+      <c r="D3" s="62" t="n"/>
+      <c r="E3" s="62" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="63" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="B4" s="63" t="inlineStr">
+        <is>
+          <t>文件</t>
+        </is>
+      </c>
+      <c r="C4" s="63" t="inlineStr">
+        <is>
+          <t>SHA-256</t>
+        </is>
+      </c>
+      <c r="D4" s="63" t="inlineStr">
+        <is>
+          <t>覆盖范围</t>
+        </is>
+      </c>
+      <c r="E4" s="63" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="62" t="inlineStr">
+        <is>
+          <t>A 厂商回函</t>
+        </is>
+      </c>
+      <c r="B5" s="62" t="inlineStr">
+        <is>
+          <t>21 项逐项回函工作簿（未入库）</t>
+        </is>
+      </c>
+      <c r="C5" s="62" t="inlineStr">
+        <is>
+          <t>7ff7f7343295397bc4b138a9233b9b64d7087c139153ed5a7d7a728a9d1d6133</t>
+        </is>
+      </c>
+      <c r="D5" s="62" t="inlineStr">
+        <is>
+          <t>21 项；含 6.0.3/6.3 版本矩阵、AIGS 演进页</t>
+        </is>
+      </c>
+      <c r="E5" s="62" t="inlineStr">
+        <is>
+          <t>产品能力、版本、路线图基线</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="62" t="inlineStr">
+        <is>
+          <t>B 内部校验回函</t>
+        </is>
+      </c>
+      <c r="B6" s="62" t="inlineStr">
+        <is>
+          <t>IAM 问询函回函 DOCX（未入库）</t>
+        </is>
+      </c>
+      <c r="C6" s="62" t="inlineStr">
+        <is>
+          <t>03c8e286412de9e7db178597f4fd8220b1e9f6a7ac1624aed20f820a2e50097f</t>
+        </is>
+      </c>
+      <c r="D6" s="62" t="inlineStr">
+        <is>
+          <t>18 项正文；§06/08/16 未填；总表与正文有冲突</t>
+        </is>
+      </c>
+      <c r="E6" s="62" t="inlineStr">
+        <is>
+          <t>部署观察、接口样例、内部验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="63" t="n"/>
+      <c r="B7" s="63" t="n"/>
+      <c r="C7" s="63" t="n"/>
+      <c r="D7" s="63" t="n"/>
+      <c r="E7" s="63" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="62" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B8" s="62" t="inlineStr">
+        <is>
+          <t>事项</t>
+        </is>
+      </c>
+      <c r="C8" s="62" t="inlineStr">
+        <is>
+          <t>A 厂商回函</t>
+        </is>
+      </c>
+      <c r="D8" s="62" t="inlineStr">
+        <is>
+          <t>B 内部校验回函</t>
+        </is>
+      </c>
+      <c r="E8" s="62" t="inlineStr">
+        <is>
+          <t>当前采用口径（V1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="62" t="inlineStr">
+        <is>
+          <t>C-01</t>
+        </is>
+      </c>
+      <c r="B9" s="62" t="inlineStr">
+        <is>
+          <t>公共客户端/PKCE</t>
+        </is>
+      </c>
+      <c r="C9" s="62" t="inlineStr">
+        <is>
+          <t>6.0.3/6.3 均不支持公共客户端与 PKCE S256；换票 secret 必需</t>
+        </is>
+      </c>
+      <c r="D9" s="62" t="inlineStr">
+        <is>
+          <t>§02 称授权码 PKCE 能力具备（允许 plain）；§08 未填写，未确认免 Secret 公共客户端</t>
+        </is>
+      </c>
+      <c r="E9" s="62" t="inlineStr">
+        <is>
+          <t>按机密客户端 + 系统钥匙串；不宣称公共客户端/PKCE；PKCE 仅留后续开关</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="62" t="inlineStr">
+        <is>
+          <t>C-02</t>
+        </is>
+      </c>
+      <c r="B10" s="62" t="inlineStr">
+        <is>
+          <t>已发 AT 停用阻断</t>
+        </is>
+      </c>
+      <c r="C10" s="62" t="inlineStr">
+        <is>
+          <t>“需产品确认，按不具备规划”；建议短 TTL + 网关侧校验 + 高敏二次确认</t>
+        </is>
+      </c>
+      <c r="D10" s="62" t="inlineStr">
+        <is>
+          <t>账号禁用后 AT/RT 实时作废；网关经有效性校验接口感知</t>
+        </is>
+      </c>
+      <c r="E10" s="62" t="inlineStr">
+        <is>
+          <t>按未证实处理；不承诺五分钟；以短 TTL、有效性回查、管理台强制下线组合并实测</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="62" t="inlineStr">
+        <is>
+          <t>C-03</t>
+        </is>
+      </c>
+      <c r="B11" s="62" t="inlineStr">
+        <is>
+          <t>RP 登出与全局 SSO</t>
+        </is>
+      </c>
+      <c r="C11" s="62" t="inlineStr">
+        <is>
+          <t>6.0.3 不支持、6.3 部分支持；单点登出原生能力有，但标准 RP 登出边界待确认</t>
+        </is>
+      </c>
+      <c r="D11" s="62" t="inlineStr">
+        <is>
+          <t>支持 RP-Initiated Logout、不强制 id_token_hint；能否彻底终结全局 SSO 仍是待答问题</t>
+        </is>
+      </c>
+      <c r="E11" s="62" t="inlineStr">
+        <is>
+          <t>默认只做本地清理 + 当前授权退出；全局 SSO 登出只作兜底，不替代单授权撤销</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="62" t="inlineStr">
+        <is>
+          <t>C-04</t>
+        </is>
+      </c>
+      <c r="B12" s="62" t="inlineStr">
+        <is>
+          <t>用户类型暴露</t>
+        </is>
+      </c>
+      <c r="C12" s="62" t="inlineStr">
+        <is>
+          <t>由记录来源决定，未见独立字段或 UserInfo 暴露</t>
+        </is>
+      </c>
+      <c r="D12" s="62" t="inlineStr">
+        <is>
+          <t>正文明确未在 ID Token 或 UserInfo 暴露；整理稿曾误写“可经 UserInfo 返回”，已回退</t>
+        </is>
+      </c>
+      <c r="E12" s="62" t="inlineStr">
+        <is>
+          <t>按未暴露处理；字段名、枚举、刷新时效待契约</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="62" t="inlineStr">
+        <is>
+          <t>C-05</t>
+        </is>
+      </c>
+      <c r="B13" s="62" t="inlineStr">
+        <is>
+          <t>SCIM 出站</t>
+        </is>
+      </c>
+      <c r="C13" s="62" t="inlineStr">
+        <is>
+          <t>6.0.3 不支持；6.3 部分支持；AIGS 有 SCIM 端点但需上游推送</t>
+        </is>
+      </c>
+      <c r="D13" s="62" t="inlineStr">
+        <is>
+          <t>18 项正文未覆盖</t>
+        </is>
+      </c>
+      <c r="E13" s="62" t="inlineStr">
+        <is>
+          <t>V1 不做目录同步；P2 前验证 6.3 或桥接；不把 AIGS 当补丁</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="62" t="inlineStr">
+        <is>
+          <t>C-06</t>
+        </is>
+      </c>
+      <c r="B14" s="62" t="inlineStr">
+        <is>
+          <t>回调匹配</t>
+        </is>
+      </c>
+      <c r="C14" s="62" t="inlineStr">
+        <is>
+          <t>D 列称精确匹配；H 列称支持动态端口（RFC 8252 §7.3），自相矛盾</t>
+        </is>
+      </c>
+      <c r="D14" s="62" t="inlineStr">
+        <is>
+          <t>§02 称前缀匹配、端口可动态分配、路径无法严格校验</t>
+        </is>
+      </c>
+      <c r="E14" s="62" t="inlineStr">
+        <is>
+          <t>固定端口 + 精确登记优先；动态端口需配置与反向用例；未证实前不开放</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="62" t="inlineStr">
+        <is>
+          <t>C-07</t>
+        </is>
+      </c>
+      <c r="B15" s="62" t="inlineStr">
+        <is>
+          <t>并发刷新</t>
+        </is>
+      </c>
+      <c r="C15" s="62" t="inlineStr">
+        <is>
+          <t>服务端不做并发互斥；多端策略 D/H 列矛盾（无策略控制 vs 三档互踢）</t>
+        </is>
+      </c>
+      <c r="D15" s="62" t="inlineStr">
+        <is>
+          <t>§06 未填写</t>
+        </is>
+      </c>
+      <c r="E15" s="62" t="inlineStr">
+        <is>
+          <t>客户端 single-flight；服务端返回、重用误杀、跨端影响联调实测</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="62" t="inlineStr">
+        <is>
+          <t>C-08</t>
+        </is>
+      </c>
+      <c r="B16" s="62" t="inlineStr">
+        <is>
+          <t>错误码/限流</t>
+        </is>
+      </c>
+      <c r="C16" s="62" t="inlineStr">
+        <is>
+          <t>标准错误码集；限流、Retry-After、状态映射随对接文档交付</t>
+        </is>
+      </c>
+      <c r="D16" s="62" t="inlineStr">
+        <is>
+          <t>§16 未填写；所谓 5 个实测场景不在两份原始回函正文</t>
+        </is>
+      </c>
+      <c r="E16" s="62" t="inlineStr">
+        <is>
+          <t>不以 200/302 判定成功；错误码全表、429/Retry-After、超时行为待补</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/plans/dsh-plugin-tools/iam-response-analysis.xlsx
+++ b/docs/plans/dsh-plugin-tools/iam-response-analysis.xlsx
@@ -957,7 +957,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1125,7 +1124,6 @@
       <c r="E14" s="10" t="n"/>
       <c r="F14" s="11" t="n"/>
     </row>
-    <row r="15"/>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -1181,7 +1179,6 @@
       <c r="E20" s="10" t="n"/>
       <c r="F20" s="11" t="n"/>
     </row>
-    <row r="21"/>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
@@ -1573,7 +1570,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
@@ -1763,7 +1759,6 @@
       <c r="E50" s="10" t="n"/>
       <c r="F50" s="11" t="n"/>
     </row>
-    <row r="51"/>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
@@ -1963,7 +1958,6 @@
       <c r="E60" s="10" t="n"/>
       <c r="F60" s="11" t="n"/>
     </row>
-    <row r="61"/>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
@@ -2031,7 +2025,6 @@
       <c r="E67" s="10" t="n"/>
       <c r="F67" s="11" t="n"/>
     </row>
-    <row r="68"/>
     <row r="69" ht="34" customHeight="1">
       <c r="A69" s="20" t="inlineStr">
         <is>
@@ -2044,7 +2037,6 @@
       <c r="E69" s="10" t="n"/>
       <c r="F69" s="11" t="n"/>
     </row>
-    <row r="70"/>
     <row r="71">
       <c r="A71" s="59" t="inlineStr">
         <is>
@@ -2178,7 +2170,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
         <is>
@@ -2189,7 +2180,6 @@
       <c r="C4" s="10" t="n"/>
       <c r="D4" s="11" t="n"/>
     </row>
-    <row r="5"/>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -2339,7 +2329,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
@@ -2455,7 +2444,6 @@
       </c>
       <c r="D21" s="11" t="n"/>
     </row>
-    <row r="22"/>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
@@ -2561,7 +2549,6 @@
       </c>
       <c r="D29" s="11" t="n"/>
     </row>
-    <row r="30"/>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
@@ -3135,7 +3122,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -3382,7 +3368,7 @@
       </c>
       <c r="D8" s="44" t="inlineStr">
         <is>
-          <t>HR/AD/LDAP 同步原生，含日志、异源对账、分级告警；与权威源“实时同步”，数据回补为每日 23:00 文件拉取、可手动触发；账号状态更新后认证阻隔实时。已签发 AT 的服务端实时阻断明确为“需产品确认，按不具备规划”，补偿为短 TTL + 网关状态校验 + 高敏操作二次确认。</t>
+          <t>HR/AD/LDAP 同步原生，含日志、异源对账、分级告警；与权威源“实时同步”，数据回补为每日 23:00 文件拉取、可手动触发；账号状态更新后认证阻隔实时。已签发 AT 的服务端实时阻断按“需产品确认、不具备规划”处理，补偿为短 TTL + 网关状态校验 + 高敏操作二次确认。</t>
         </is>
       </c>
       <c r="E8" s="42" t="inlineStr">
@@ -3439,7 +3425,7 @@
       </c>
       <c r="D9" s="39" t="inlineStr">
         <is>
-          <t>AT 默认 7200 秒、最大生命周期 7200 秒、可配；客户端级可独立配置 AT/RT/会话有效期。TGT Refresh on Check 滑动续期并受最大有效期约束，TGT 默认 24 小时。管理台“在线应用 Token 管理”可查登录时间/过期时间/IP/设备/协议/应用/账号/二次认证方式，支持下线所有/当前/其他令牌。多端策略三档、设备上限可配。RT 默认 2 小时、可配、未设绝对最长寿命。</t>
+          <t>AT 默认 7200 秒、最大生命周期 7200 秒、可配；客户端级可独立配置 AT/RT/会话有效期。TGT Refresh on Check 滑动续期并受最大有效期约束，TGT 默认 24 小时。管理台“在线应用 Token 管理”可查登录时间/过期时间/IP/设备/协议/应用/账号/二次认证方式，支持下线所有/当前/其他令牌。多端策略三档、设备上限可配。RT 默认 2 小时、可配、绝对最长寿命未说明。</t>
         </is>
       </c>
       <c r="E9" s="40" t="inlineStr">
@@ -3952,7 +3938,7 @@
       </c>
       <c r="D18" s="44" t="inlineStr">
         <is>
-          <t>单点登出为产品原生能力（注销后经统一退出页注销各纳管应用），注销范围当前/其他/全部；标准 RP-Initiated Logout、id_token_hint、post_logout_redirect_uri、Back-Channel/Session Management、prompt=login/max_age 文档未载明。业务边界：本地清空全部令牌 + 跳转 IAM 登出地址终结 SSO。</t>
+          <t>单点登出为产品原生能力（注销后经统一退出页注销各纳管应用），注销范围当前/其他/全部；标准 RP-Initiated Logout、id_token_hint、post_logout_redirect_uri、Back-Channel/Session Management、prompt=login/max_age 文档未载明。建议业务边界（非回函已确认能力）：本地清空全部令牌 + 跳转 IAM 登出地址终结 SSO。</t>
         </is>
       </c>
       <c r="E18" s="45" t="inlineStr">
@@ -4390,7 +4376,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="48" t="inlineStr">
         <is>
@@ -4446,7 +4431,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -7499,7 +7483,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -8024,7 +8007,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -8331,7 +8313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8697,6 +8679,33 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="62" t="inlineStr">
+        <is>
+          <t>C-09</t>
+        </is>
+      </c>
+      <c r="B17" s="62" t="inlineStr">
+        <is>
+          <t>目录同步时延</t>
+        </is>
+      </c>
+      <c r="C17" s="62" t="inlineStr">
+        <is>
+          <t>称与权威源实时同步，未给量化时延；回补为每日 23:00 文件拉取、可手动触发</t>
+        </is>
+      </c>
+      <c r="D17" s="62" t="inlineStr">
+        <is>
+          <t>正式员工 HR 增量 30 分钟生成、IAM 每小时拉取，最坏 90 分钟；供应商员工 MQ 实时；账号禁用后 AT/RT 实时作废</t>
+        </is>
+      </c>
+      <c r="E17" s="62" t="inlineStr">
+        <is>
+          <t>规划取 90 分钟上限并实测；不把“实时同步”当五分钟证据；供应商与正式员工分开核算</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
